--- a/survey_templates/039_gsco_family_participation_survey--survey_templates.xlsx
+++ b/survey_templates/039_gsco_family_participation_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_1</t>
+          <t>family_level_of_comfort</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>family level of comfort</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Family level of comfort with in-person events</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Rate your comfort level with participating in in-person events</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,20 +542,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_2</t>
+          <t>event_frequency</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>troop model</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Frequency of in-person event participation</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>How often do you participate in events that are in-person?</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,20 +569,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_3</t>
+          <t>event_type</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Type of event</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>What type of event is your family most likely to participate in?</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_4</t>
+          <t>participation_method</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>family level of comfort</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How do you usually participate in events with your family?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>How do you usually participate in events with your family?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_5</t>
+          <t>typical_participation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Typical family event participation</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Describe your typical family event participation</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_6</t>
+          <t>day_of_week</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Day of the week for family events</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>What day of the week do you usually participate in family events?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_7</t>
+          <t>time_of_participation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Time of day for family events</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>At what time do you usually participate in family events?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_8</t>
+          <t>event_days</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Event Days</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Do you usually participate in family events on weekdays or weekends?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_9</t>
+          <t>communication_methods</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Communication methods with family members</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>What type of communication methods do you usually use with family members?</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_10</t>
+          <t>communication_frequency</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Frequency of communication with family members</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>How often do you communicate with family members?</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_11</t>
+          <t>time_zone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Time zone for family events</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>What time zone do you usually participate in family events?</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,320 +812,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_12</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Describe your family's event participation</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>form_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>form_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>form_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>form_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>form_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>form_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>form_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>form_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,85 +875,272 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_2_choices</t>
+          <t>event_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>in-person</t>
+          <t>event_with_friends</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>in-person</t>
+          <t>Event with friends</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_2_choices</t>
+          <t>event_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>virtual</t>
+          <t>event_with_family</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>virtual</t>
+          <t>Event with family</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_2_choices</t>
+          <t>event_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>event_with_a_mix_of_both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>Event with a mix of both</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_5_choices</t>
+          <t>event_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no_preference</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No preference</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_5_choices</t>
+          <t>participation_method_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>In-person</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>participation_method_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>virtual</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>participation_method_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>participation_method_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>no_preference</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>No preference</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>event_days_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>weekdays</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Weekdays</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>event_days_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>weekends</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Weekends</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>communication_methods_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>calls</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Calls</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>communication_methods_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>messages</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Messages</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>communication_methods_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>emails</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Emails</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>communication_methods_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>video_calls</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Video calls</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>communication_methods_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>social_media</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Social media</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>communication_methods_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>in-person</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>In-person</t>
         </is>
       </c>
     </row>
